--- a/outputs/56915.xlsx
+++ b/outputs/56915.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="24">
   <si>
     <t xml:space="preserve"> </t>
   </si>
@@ -48,6 +48,9 @@
     <t xml:space="preserve">    TOTAL: REVENUE</t>
   </si>
   <si>
+    <t xml:space="preserve">1.00</t>
+  </si>
+  <si>
     <t xml:space="preserve">    COST OF GOODS SOLD</t>
   </si>
   <si>
@@ -57,10 +60,19 @@
     <t xml:space="preserve">        STUFF 1</t>
   </si>
   <si>
+    <t xml:space="preserve">0.03</t>
+  </si>
+  <si>
     <t xml:space="preserve">        STUFF 2</t>
   </si>
   <si>
+    <t xml:space="preserve">(0.00)</t>
+  </si>
+  <si>
     <t xml:space="preserve">        STUFF 3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.07</t>
   </si>
   <si>
     <t xml:space="preserve">Total</t>
@@ -88,12 +100,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="5">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="General"/>
-    <numFmt numFmtId="165" formatCode="#,##0.00;\(#,##0.00\);0.00"/>
-    <numFmt numFmtId="166" formatCode="0%"/>
-    <numFmt numFmtId="167" formatCode="0.00%"/>
-    <numFmt numFmtId="168" formatCode="#,##0.00;\(#,##0.00\)"/>
+    <numFmt numFmtId="165" formatCode="#,##0.00;\(#,##0.00\)"/>
+    <numFmt numFmtId="166" formatCode="0.00%"/>
   </numFmts>
   <fonts count="14">
     <font>
@@ -283,197 +293,174 @@
     <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="42">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="9" fillId="2" borderId="3" xfId="19" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="9" fillId="2" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="9" fillId="2" borderId="0" xfId="19" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="13" fillId="2" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="9" fillId="2" borderId="0" xfId="19" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="6" fillId="2" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="9" fillId="2" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="9" fillId="2" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="11" fillId="2" borderId="0" xfId="19" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="9" fillId="2" borderId="0" xfId="19" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="9" fillId="2" borderId="0" xfId="19" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="12" fillId="2" borderId="0" xfId="19" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="168" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="9" fillId="2" borderId="0" xfId="19" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="168" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="9" fillId="2" borderId="3" xfId="19" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="13" fillId="2" borderId="3" xfId="19" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="168" fontId="6" fillId="2" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="168" fontId="9" fillId="2" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="9" fillId="2" borderId="5" xfId="19" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="13" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="168" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="13" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="13" fillId="2" borderId="0" xfId="19" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="13" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -729,210 +716,170 @@
   <dimension ref="A1:E23"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="34.11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="34.11"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1"/>
+      <c r="A1" s="2"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1"/>
-    </row>
-    <row r="3" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2"/>
-    </row>
-    <row r="4" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2"/>
-    </row>
-    <row r="5" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="2"/>
-    </row>
-    <row r="6" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="2"/>
-    </row>
-    <row r="7" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="3"/>
-    </row>
-    <row r="8" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="3"/>
-    </row>
-    <row r="9" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="3"/>
-    </row>
-    <row r="10" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="3"/>
-    </row>
-    <row r="11" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="4" t="s">
+      <c r="A2" s="2"/>
+    </row>
+    <row r="3" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="3"/>
+    </row>
+    <row r="4" customFormat="false" ht="13.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="3"/>
+    </row>
+    <row r="5" customFormat="false" ht="13.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="3"/>
+    </row>
+    <row r="6" customFormat="false" ht="13.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="3"/>
+    </row>
+    <row r="7" customFormat="false" ht="13.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="4"/>
+    </row>
+    <row r="8" customFormat="false" ht="13.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="4"/>
+    </row>
+    <row r="9" customFormat="false" ht="13.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="4"/>
+    </row>
+    <row r="10" customFormat="false" ht="13.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="4"/>
+    </row>
+    <row r="11" customFormat="false" ht="13.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="5" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="5" t="s">
+    <row r="12" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="B12" s="6" t="s">
+      <c r="B12" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="C12" s="6"/>
-      <c r="D12" s="6"/>
-      <c r="E12" s="6"/>
-    </row>
-    <row r="13" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="7" t="s">
+      <c r="C12" s="7"/>
+      <c r="D12" s="7"/>
+      <c r="E12" s="7"/>
+    </row>
+    <row r="13" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B13" s="8" t="s">
+      <c r="B13" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="C13" s="9" t="s">
+      <c r="C13" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="D13" s="8" t="s">
+      <c r="D13" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="E13" s="9" t="s">
+      <c r="E13" s="10" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="10"/>
-    </row>
-    <row r="15" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="11"/>
-    </row>
-    <row r="16" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="12" t="s">
+    <row r="14" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="11"/>
+    </row>
+    <row r="15" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="12"/>
+    </row>
+    <row r="16" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="13" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="13"/>
-    </row>
-    <row r="18" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="14" t="s">
+    <row r="17" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="14"/>
+    </row>
+    <row r="18" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="B18" s="15" t="n">
-        <f aca="false">ROUND(INDEX(DATA!$F$18:$F$24,MATCH($A18,DATA!$A$18:$A$24,0)),2)</f>
+      <c r="B18" s="16" t="n">
         <v>56113.91</v>
       </c>
-      <c r="C18" s="16" t="n">
-        <f aca="false">ROUND(INDEX(DATA!$G$18:$G$24,MATCH($A18,DATA!$A$18:$A$24,0)),2)</f>
-        <v>1</v>
-      </c>
-      <c r="D18" s="15" t="n">
-        <f aca="false">ROUND(INDEX(DATA!$H$18:$H$24,MATCH($A18,DATA!$A$18:$A$24,0)),2)</f>
+      <c r="C18" s="17" t="s">
+        <v>8</v>
+      </c>
+      <c r="D18" s="16" t="n">
         <v>56113.91</v>
       </c>
-      <c r="E18" s="16" t="n">
-        <f aca="false">ROUND(INDEX(DATA!$I$18:$I$24,MATCH($A18,DATA!$A$18:$A$24,0)),2)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="10" t="s">
+      <c r="E18" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="B19" s="17" t="n">
-        <f aca="false">ROUND(INDEX(DATA!$F$18:$F$24,MATCH($A19,DATA!$A$18:$A$24,0)),2)</f>
-        <v>0</v>
-      </c>
-      <c r="C19" s="18" t="n">
-        <f aca="false">ROUND(INDEX(DATA!$G$18:$G$24,MATCH($A19,DATA!$A$18:$A$24,0)),2)</f>
-        <v>0</v>
-      </c>
-      <c r="D19" s="17" t="n">
-        <f aca="false">ROUND(INDEX(DATA!$H$18:$H$24,MATCH($A19,DATA!$A$18:$A$24,0)),2)</f>
-        <v>0</v>
-      </c>
-      <c r="E19" s="18" t="n">
-        <f aca="false">ROUND(INDEX(DATA!$I$18:$I$24,MATCH($A19,DATA!$A$18:$A$24,0)),2)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="10" t="s">
+    </row>
+    <row r="19" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="B20" s="17" t="n">
-        <f aca="false">ROUND(INDEX(DATA!$F$18:$F$24,MATCH($A20,DATA!$A$18:$A$24,0)),2)</f>
-        <v>0</v>
-      </c>
-      <c r="C20" s="18" t="n">
-        <f aca="false">ROUND(INDEX(DATA!$G$18:$G$24,MATCH($A20,DATA!$A$18:$A$24,0)),2)</f>
-        <v>0</v>
-      </c>
-      <c r="D20" s="17" t="n">
-        <f aca="false">ROUND(INDEX(DATA!$H$18:$H$24,MATCH($A20,DATA!$A$18:$A$24,0)),2)</f>
-        <v>0</v>
-      </c>
-      <c r="E20" s="18" t="n">
-        <f aca="false">ROUND(INDEX(DATA!$I$18:$I$24,MATCH($A20,DATA!$A$18:$A$24,0)),2)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="10" t="s">
+      <c r="B19" s="4"/>
+      <c r="C19" s="18"/>
+      <c r="D19" s="4"/>
+      <c r="E19" s="18"/>
+    </row>
+    <row r="20" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="11" t="s">
         <v>10</v>
       </c>
+      <c r="B20" s="4"/>
+      <c r="C20" s="18"/>
+      <c r="D20" s="4"/>
+      <c r="E20" s="18"/>
+    </row>
+    <row r="21" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="11" t="s">
+        <v>11</v>
+      </c>
       <c r="B21" s="19" t="n">
-        <f aca="false">ROUND(INDEX(DATA!$F$18:$F$24,MATCH($A21,DATA!$A$18:$A$24,0)),2)</f>
         <v>1705.66</v>
       </c>
-      <c r="C21" s="20" t="n">
-        <f aca="false">ROUND(INDEX(DATA!$G$18:$G$24,MATCH($A21,DATA!$A$18:$A$24,0)),2)</f>
-        <v>0.03</v>
+      <c r="C21" s="20" t="s">
+        <v>12</v>
       </c>
       <c r="D21" s="19" t="n">
-        <f aca="false">ROUND(INDEX(DATA!$H$18:$H$24,MATCH($A21,DATA!$A$18:$A$24,0)),2)</f>
         <v>1705.66</v>
       </c>
-      <c r="E21" s="20" t="n">
-        <f aca="false">ROUND(INDEX(DATA!$I$18:$I$24,MATCH($A21,DATA!$A$18:$A$24,0)),2)</f>
-        <v>0.03</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="10" t="s">
-        <v>11</v>
+      <c r="E21" s="20" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="11" t="s">
+        <v>13</v>
       </c>
       <c r="B22" s="19" t="n">
-        <f aca="false">ROUND(INDEX(DATA!$F$18:$F$24,MATCH($A22,DATA!$A$18:$A$24,0)),2)</f>
         <v>-95.68</v>
       </c>
-      <c r="C22" s="20" t="n">
-        <f aca="false">ROUND(INDEX(DATA!$G$18:$G$24,MATCH($A22,DATA!$A$18:$A$24,0)),2)</f>
-        <v>-0</v>
+      <c r="C22" s="20" t="s">
+        <v>14</v>
       </c>
       <c r="D22" s="19" t="n">
-        <f aca="false">ROUND(INDEX(DATA!$H$18:$H$24,MATCH($A22,DATA!$A$18:$A$24,0)),2)</f>
         <v>-95.68</v>
       </c>
-      <c r="E22" s="20" t="n">
-        <f aca="false">ROUND(INDEX(DATA!$I$18:$I$24,MATCH($A22,DATA!$A$18:$A$24,0)),2)</f>
-        <v>-0</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="10" t="s">
-        <v>12</v>
+      <c r="E22" s="20" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="11" t="s">
+        <v>15</v>
       </c>
       <c r="B23" s="19" t="n">
-        <f aca="false">ROUND(INDEX(DATA!$F$18:$F$24,MATCH($A23,DATA!$A$18:$A$24,0)),2)</f>
         <v>3658.2</v>
       </c>
-      <c r="C23" s="20" t="n">
-        <f aca="false">ROUND(INDEX(DATA!$G$18:$G$24,MATCH($A23,DATA!$A$18:$A$24,0)),2)</f>
-        <v>0.07</v>
+      <c r="C23" s="20" t="s">
+        <v>16</v>
       </c>
       <c r="D23" s="19" t="n">
-        <f aca="false">ROUND(INDEX(DATA!$H$18:$H$24,MATCH($A23,DATA!$A$18:$A$24,0)),2)</f>
         <v>3658.2</v>
       </c>
-      <c r="E23" s="20" t="n">
-        <f aca="false">ROUND(INDEX(DATA!$I$18:$I$24,MATCH($A23,DATA!$A$18:$A$24,0)),2)</f>
-        <v>0.07</v>
+      <c r="E23" s="20" t="s">
+        <v>16</v>
       </c>
     </row>
   </sheetData>
@@ -957,13 +904,13 @@
   <dimension ref="A1:AC24"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="34.11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="12.11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="12.56"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="34.11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="12.11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="12.56"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1"/>
+      <c r="A1" s="2"/>
       <c r="B1" s="21"/>
       <c r="C1" s="21"/>
       <c r="D1" s="21"/>
@@ -994,7 +941,7 @@
       <c r="AC1" s="23"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1"/>
+      <c r="A2" s="2"/>
       <c r="B2" s="21"/>
       <c r="C2" s="21"/>
       <c r="D2" s="21"/>
@@ -1024,8 +971,8 @@
       <c r="AB2" s="23"/>
       <c r="AC2" s="23"/>
     </row>
-    <row r="3" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2"/>
+    <row r="3" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="3"/>
       <c r="B3" s="21"/>
       <c r="C3" s="21"/>
       <c r="D3" s="21"/>
@@ -1055,8 +1002,8 @@
       <c r="AB3" s="23"/>
       <c r="AC3" s="23"/>
     </row>
-    <row r="4" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2"/>
+    <row r="4" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="3"/>
       <c r="B4" s="21"/>
       <c r="C4" s="21"/>
       <c r="D4" s="21"/>
@@ -1086,8 +1033,8 @@
       <c r="AB4" s="23"/>
       <c r="AC4" s="23"/>
     </row>
-    <row r="5" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="2"/>
+    <row r="5" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="3"/>
       <c r="B5" s="21"/>
       <c r="C5" s="21"/>
       <c r="D5" s="21"/>
@@ -1117,8 +1064,8 @@
       <c r="AB5" s="23"/>
       <c r="AC5" s="23"/>
     </row>
-    <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="2"/>
+    <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="3"/>
       <c r="B6" s="21"/>
       <c r="C6" s="21"/>
       <c r="D6" s="21"/>
@@ -1148,8 +1095,8 @@
       <c r="AB6" s="23"/>
       <c r="AC6" s="23"/>
     </row>
-    <row r="7" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="3"/>
+    <row r="7" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="4"/>
       <c r="B7" s="21"/>
       <c r="C7" s="21"/>
       <c r="D7" s="21"/>
@@ -1160,8 +1107,8 @@
       <c r="I7" s="24"/>
       <c r="J7" s="21"/>
       <c r="K7" s="24"/>
-      <c r="L7" s="25"/>
-      <c r="M7" s="25"/>
+      <c r="L7" s="18"/>
+      <c r="M7" s="18"/>
       <c r="N7" s="21"/>
       <c r="O7" s="24"/>
       <c r="P7" s="23"/>
@@ -1179,8 +1126,8 @@
       <c r="AB7" s="23"/>
       <c r="AC7" s="23"/>
     </row>
-    <row r="8" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="3"/>
+    <row r="8" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="4"/>
       <c r="B8" s="21"/>
       <c r="C8" s="21"/>
       <c r="D8" s="21"/>
@@ -1191,8 +1138,8 @@
       <c r="I8" s="24"/>
       <c r="J8" s="21"/>
       <c r="K8" s="24"/>
-      <c r="L8" s="25"/>
-      <c r="M8" s="25"/>
+      <c r="L8" s="18"/>
+      <c r="M8" s="18"/>
       <c r="N8" s="21"/>
       <c r="O8" s="24"/>
       <c r="P8" s="23"/>
@@ -1210,8 +1157,8 @@
       <c r="AB8" s="23"/>
       <c r="AC8" s="23"/>
     </row>
-    <row r="9" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="3"/>
+    <row r="9" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="4"/>
       <c r="B9" s="21"/>
       <c r="C9" s="21"/>
       <c r="D9" s="21"/>
@@ -1222,8 +1169,8 @@
       <c r="I9" s="24"/>
       <c r="J9" s="21"/>
       <c r="K9" s="24"/>
-      <c r="L9" s="25"/>
-      <c r="M9" s="25"/>
+      <c r="L9" s="18"/>
+      <c r="M9" s="18"/>
       <c r="N9" s="21"/>
       <c r="O9" s="24"/>
       <c r="P9" s="23"/>
@@ -1241,8 +1188,8 @@
       <c r="AB9" s="23"/>
       <c r="AC9" s="23"/>
     </row>
-    <row r="10" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="3"/>
+    <row r="10" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="4"/>
       <c r="B10" s="21"/>
       <c r="C10" s="21"/>
       <c r="D10" s="21"/>
@@ -1255,8 +1202,8 @@
       <c r="I10" s="24"/>
       <c r="J10" s="21"/>
       <c r="K10" s="24"/>
-      <c r="L10" s="25"/>
-      <c r="M10" s="25"/>
+      <c r="L10" s="18"/>
+      <c r="M10" s="18"/>
       <c r="N10" s="21"/>
       <c r="O10" s="24"/>
       <c r="P10" s="23"/>
@@ -1274,8 +1221,8 @@
       <c r="AB10" s="23"/>
       <c r="AC10" s="23"/>
     </row>
-    <row r="11" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="4" t="s">
+    <row r="11" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="5" t="s">
         <v>0</v>
       </c>
       <c r="B11" s="21"/>
@@ -1307,718 +1254,718 @@
       <c r="AB11" s="23"/>
       <c r="AC11" s="23"/>
     </row>
-    <row r="12" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="26" t="s">
+    <row r="12" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="25" t="s">
         <v>0</v>
       </c>
-      <c r="B12" s="27" t="s">
+      <c r="B12" s="26" t="s">
+        <v>17</v>
+      </c>
+      <c r="C12" s="26"/>
+      <c r="D12" s="26"/>
+      <c r="E12" s="26"/>
+      <c r="F12" s="27" t="s">
+        <v>2</v>
+      </c>
+      <c r="G12" s="27"/>
+      <c r="H12" s="27"/>
+      <c r="I12" s="27"/>
+      <c r="J12" s="27" t="s">
+        <v>18</v>
+      </c>
+      <c r="K12" s="27"/>
+      <c r="L12" s="27"/>
+      <c r="M12" s="27"/>
+      <c r="N12" s="27" t="s">
+        <v>19</v>
+      </c>
+      <c r="O12" s="27"/>
+      <c r="P12" s="27"/>
+      <c r="Q12" s="27"/>
+      <c r="R12" s="27" t="s">
+        <v>20</v>
+      </c>
+      <c r="S12" s="27"/>
+      <c r="T12" s="27"/>
+      <c r="U12" s="27"/>
+      <c r="V12" s="26" t="s">
+        <v>21</v>
+      </c>
+      <c r="W12" s="26"/>
+      <c r="X12" s="26"/>
+      <c r="Y12" s="26"/>
+      <c r="Z12" s="26" t="s">
+        <v>22</v>
+      </c>
+      <c r="AA12" s="26"/>
+      <c r="AB12" s="26"/>
+      <c r="AC12" s="26"/>
+    </row>
+    <row r="13" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B13" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="C13" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="D13" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="E13" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="F13" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="G13" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="H13" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="I13" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="J13" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="K13" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="L13" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="M13" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="N13" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="O13" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="P13" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q13" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="R13" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="S13" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="T13" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="U13" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="V13" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="W13" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="X13" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y13" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z13" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA13" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB13" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC13" s="10" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="11"/>
+      <c r="B14" s="28"/>
+      <c r="C14" s="29"/>
+      <c r="D14" s="28"/>
+      <c r="E14" s="29"/>
+      <c r="F14" s="28"/>
+      <c r="G14" s="29"/>
+      <c r="H14" s="28"/>
+      <c r="I14" s="29"/>
+      <c r="J14" s="28"/>
+      <c r="K14" s="29"/>
+      <c r="L14" s="28"/>
+      <c r="M14" s="29"/>
+      <c r="N14" s="28"/>
+      <c r="O14" s="29"/>
+      <c r="P14" s="28"/>
+      <c r="Q14" s="29"/>
+      <c r="R14" s="28"/>
+      <c r="S14" s="29"/>
+      <c r="T14" s="28"/>
+      <c r="U14" s="29"/>
+      <c r="V14" s="28"/>
+      <c r="W14" s="29"/>
+      <c r="X14" s="28"/>
+      <c r="Y14" s="29"/>
+      <c r="Z14" s="28"/>
+      <c r="AA14" s="29"/>
+      <c r="AB14" s="28"/>
+      <c r="AC14" s="29"/>
+    </row>
+    <row r="15" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="12"/>
+      <c r="B15" s="12"/>
+      <c r="C15" s="30"/>
+      <c r="D15" s="12"/>
+      <c r="E15" s="30"/>
+      <c r="F15" s="12"/>
+      <c r="G15" s="31"/>
+      <c r="H15" s="31"/>
+      <c r="I15" s="31"/>
+      <c r="J15" s="12"/>
+      <c r="K15" s="31"/>
+      <c r="L15" s="31"/>
+      <c r="M15" s="31"/>
+      <c r="N15" s="12"/>
+      <c r="O15" s="31"/>
+      <c r="P15" s="31"/>
+      <c r="Q15" s="31"/>
+      <c r="R15" s="12"/>
+      <c r="S15" s="31"/>
+      <c r="T15" s="31"/>
+      <c r="U15" s="31"/>
+      <c r="V15" s="12"/>
+      <c r="W15" s="31"/>
+      <c r="X15" s="31"/>
+      <c r="Y15" s="31"/>
+      <c r="Z15" s="12"/>
+      <c r="AA15" s="31"/>
+      <c r="AB15" s="31"/>
+      <c r="AC15" s="31"/>
+    </row>
+    <row r="16" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="B16" s="12"/>
+      <c r="C16" s="30"/>
+      <c r="D16" s="12"/>
+      <c r="E16" s="30"/>
+      <c r="F16" s="12"/>
+      <c r="G16" s="31"/>
+      <c r="H16" s="31"/>
+      <c r="I16" s="31"/>
+      <c r="J16" s="12"/>
+      <c r="K16" s="31"/>
+      <c r="L16" s="31"/>
+      <c r="M16" s="31"/>
+      <c r="N16" s="12"/>
+      <c r="O16" s="31"/>
+      <c r="P16" s="31"/>
+      <c r="Q16" s="31"/>
+      <c r="R16" s="12"/>
+      <c r="S16" s="31"/>
+      <c r="T16" s="31"/>
+      <c r="U16" s="31"/>
+      <c r="V16" s="12"/>
+      <c r="W16" s="31"/>
+      <c r="X16" s="31"/>
+      <c r="Y16" s="31"/>
+      <c r="Z16" s="12"/>
+      <c r="AA16" s="31"/>
+      <c r="AB16" s="31"/>
+      <c r="AC16" s="31"/>
+    </row>
+    <row r="17" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="14"/>
+      <c r="B17" s="14"/>
+      <c r="C17" s="32"/>
+      <c r="D17" s="14"/>
+      <c r="E17" s="32"/>
+      <c r="F17" s="14"/>
+      <c r="G17" s="33"/>
+      <c r="H17" s="33"/>
+      <c r="I17" s="33"/>
+      <c r="J17" s="14"/>
+      <c r="K17" s="33"/>
+      <c r="L17" s="33"/>
+      <c r="M17" s="33"/>
+      <c r="N17" s="14"/>
+      <c r="O17" s="33"/>
+      <c r="P17" s="33"/>
+      <c r="Q17" s="33"/>
+      <c r="R17" s="14"/>
+      <c r="S17" s="33"/>
+      <c r="T17" s="33"/>
+      <c r="U17" s="33"/>
+      <c r="V17" s="14"/>
+      <c r="W17" s="33"/>
+      <c r="X17" s="33"/>
+      <c r="Y17" s="33"/>
+      <c r="Z17" s="14"/>
+      <c r="AA17" s="33"/>
+      <c r="AB17" s="33"/>
+      <c r="AC17" s="33"/>
+    </row>
+    <row r="18" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="B18" s="19" t="n">
+        <v>1890146.68</v>
+      </c>
+      <c r="C18" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="D18" s="19" t="n">
+        <v>1890146.68</v>
+      </c>
+      <c r="E18" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="F18" s="16" t="n">
+        <v>56113.91</v>
+      </c>
+      <c r="G18" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H18" s="19" t="n">
+        <v>56113.91</v>
+      </c>
+      <c r="I18" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J18" s="16" t="n">
+        <v>36241.62</v>
+      </c>
+      <c r="K18" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L18" s="19" t="n">
+        <v>36241.62</v>
+      </c>
+      <c r="M18" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="N18" s="16" t="n">
+        <v>70337.43</v>
+      </c>
+      <c r="O18" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="P18" s="19" t="n">
+        <v>70337.43</v>
+      </c>
+      <c r="Q18" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="R18" s="16" t="n">
+        <v>43713.7</v>
+      </c>
+      <c r="S18" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="T18" s="19" t="n">
+        <v>43713.7</v>
+      </c>
+      <c r="U18" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="V18" s="19" t="n">
+        <v>31238.91</v>
+      </c>
+      <c r="W18" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="X18" s="19" t="n">
+        <v>31238.91</v>
+      </c>
+      <c r="Y18" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z18" s="19" t="n">
+        <v>31976.68</v>
+      </c>
+      <c r="AA18" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB18" s="19" t="n">
+        <v>31976.68</v>
+      </c>
+      <c r="AC18" s="17" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="11"/>
+      <c r="B19" s="35"/>
+      <c r="C19" s="36"/>
+      <c r="D19" s="35"/>
+      <c r="E19" s="36"/>
+      <c r="F19" s="19"/>
+      <c r="G19" s="37"/>
+      <c r="H19" s="35"/>
+      <c r="I19" s="37"/>
+      <c r="J19" s="19"/>
+      <c r="K19" s="37"/>
+      <c r="L19" s="35"/>
+      <c r="M19" s="37"/>
+      <c r="N19" s="19"/>
+      <c r="O19" s="37"/>
+      <c r="P19" s="35"/>
+      <c r="Q19" s="37"/>
+      <c r="R19" s="19"/>
+      <c r="S19" s="37"/>
+      <c r="T19" s="35"/>
+      <c r="U19" s="37"/>
+      <c r="V19" s="35"/>
+      <c r="W19" s="37"/>
+      <c r="X19" s="35"/>
+      <c r="Y19" s="37"/>
+      <c r="Z19" s="35"/>
+      <c r="AA19" s="38"/>
+      <c r="AB19" s="35"/>
+      <c r="AC19" s="37"/>
+    </row>
+    <row r="20" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="B20" s="39"/>
+      <c r="C20" s="24"/>
+      <c r="D20" s="4"/>
+      <c r="E20" s="24"/>
+      <c r="F20" s="4"/>
+      <c r="G20" s="18"/>
+      <c r="H20" s="4"/>
+      <c r="I20" s="18"/>
+      <c r="J20" s="4"/>
+      <c r="K20" s="18"/>
+      <c r="L20" s="4"/>
+      <c r="M20" s="18"/>
+      <c r="N20" s="4"/>
+      <c r="O20" s="18"/>
+      <c r="P20" s="4"/>
+      <c r="Q20" s="18"/>
+      <c r="R20" s="4"/>
+      <c r="S20" s="18"/>
+      <c r="T20" s="4"/>
+      <c r="U20" s="18"/>
+      <c r="V20" s="4"/>
+      <c r="W20" s="18"/>
+      <c r="X20" s="4"/>
+      <c r="Y20" s="18"/>
+      <c r="Z20" s="4"/>
+      <c r="AA20" s="40"/>
+      <c r="AB20" s="4"/>
+      <c r="AC20" s="18"/>
+    </row>
+    <row r="21" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="B21" s="4"/>
+      <c r="C21" s="24"/>
+      <c r="D21" s="4"/>
+      <c r="E21" s="24"/>
+      <c r="F21" s="4"/>
+      <c r="G21" s="18"/>
+      <c r="H21" s="4"/>
+      <c r="I21" s="18"/>
+      <c r="J21" s="4"/>
+      <c r="K21" s="18"/>
+      <c r="L21" s="4"/>
+      <c r="M21" s="18"/>
+      <c r="N21" s="4"/>
+      <c r="O21" s="18"/>
+      <c r="P21" s="4"/>
+      <c r="Q21" s="18"/>
+      <c r="R21" s="4"/>
+      <c r="S21" s="18"/>
+      <c r="T21" s="4"/>
+      <c r="U21" s="18"/>
+      <c r="V21" s="4"/>
+      <c r="W21" s="18"/>
+      <c r="X21" s="4"/>
+      <c r="Y21" s="18"/>
+      <c r="Z21" s="4"/>
+      <c r="AA21" s="40"/>
+      <c r="AB21" s="4"/>
+      <c r="AC21" s="18"/>
+    </row>
+    <row r="22" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="B22" s="19" t="n">
+        <v>49887.7048682951</v>
+      </c>
+      <c r="C22" s="20" t="n">
+        <v>0.0263935626775246</v>
+      </c>
+      <c r="D22" s="19" t="n">
+        <v>49887.7048682951</v>
+      </c>
+      <c r="E22" s="20" t="n">
+        <v>0.0263935626775246</v>
+      </c>
+      <c r="F22" s="19" t="n">
+        <v>1705.6561549394</v>
+      </c>
+      <c r="G22" s="20" t="n">
+        <v>0.0303963162598971</v>
+      </c>
+      <c r="H22" s="19" t="n">
+        <v>1705.6561549394</v>
+      </c>
+      <c r="I22" s="20" t="n">
+        <v>0.0303963162598971</v>
+      </c>
+      <c r="J22" s="19" t="n">
+        <v>1227.87225264468</v>
+      </c>
+      <c r="K22" s="20" t="n">
+        <v>0.0338801701647079</v>
+      </c>
+      <c r="L22" s="19" t="n">
+        <v>1227.87225264468</v>
+      </c>
+      <c r="M22" s="20" t="n">
+        <v>0.0338801701647079</v>
+      </c>
+      <c r="N22" s="19" t="n">
+        <v>2199.83862997688</v>
+      </c>
+      <c r="O22" s="20" t="n">
+        <v>0.0312755048055763</v>
+      </c>
+      <c r="P22" s="19" t="n">
+        <v>2199.83862997688</v>
+      </c>
+      <c r="Q22" s="20" t="n">
+        <v>0.0312755048055763</v>
+      </c>
+      <c r="R22" s="19" t="n">
+        <v>1232.71175827654</v>
+      </c>
+      <c r="S22" s="20" t="n">
+        <v>0.0281996664266932</v>
+      </c>
+      <c r="T22" s="19" t="n">
+        <v>1232.71175827654</v>
+      </c>
+      <c r="U22" s="20" t="n">
+        <v>0.0281996664266932</v>
+      </c>
+      <c r="V22" s="19" t="n">
+        <v>872.765729625539</v>
+      </c>
+      <c r="W22" s="20" t="n">
+        <v>0.0279384181338446</v>
+      </c>
+      <c r="X22" s="19" t="n">
+        <v>872.765729625539</v>
+      </c>
+      <c r="Y22" s="20" t="n">
+        <v>0.0279384181338446</v>
+      </c>
+      <c r="Z22" s="19" t="n">
+        <v>1231.87636658085</v>
+      </c>
+      <c r="AA22" s="41" t="n">
+        <v>0.0385242109743992</v>
+      </c>
+      <c r="AB22" s="19" t="n">
+        <v>1231.87636658085</v>
+      </c>
+      <c r="AC22" s="20" t="n">
+        <v>0.0385242109743992</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="C12" s="27"/>
-      <c r="D12" s="27"/>
-      <c r="E12" s="27"/>
-      <c r="F12" s="28" t="s">
-        <v>2</v>
-      </c>
-      <c r="G12" s="28"/>
-      <c r="H12" s="28"/>
-      <c r="I12" s="28"/>
-      <c r="J12" s="28" t="s">
-        <v>14</v>
-      </c>
-      <c r="K12" s="28"/>
-      <c r="L12" s="28"/>
-      <c r="M12" s="28"/>
-      <c r="N12" s="28" t="s">
+      <c r="B23" s="19" t="n">
+        <v>-3390.80544821547</v>
+      </c>
+      <c r="C23" s="20" t="n">
+        <v>-0.00179393773197299</v>
+      </c>
+      <c r="D23" s="19" t="n">
+        <v>-3390.80544821547</v>
+      </c>
+      <c r="E23" s="20" t="n">
+        <v>-0.00179393773197299</v>
+      </c>
+      <c r="F23" s="19" t="n">
+        <v>-95.6776850726545</v>
+      </c>
+      <c r="G23" s="20" t="n">
+        <v>-0.00170506181217196</v>
+      </c>
+      <c r="H23" s="19" t="n">
+        <v>-95.6776850726545</v>
+      </c>
+      <c r="I23" s="20" t="n">
+        <v>-0.00170506181217196</v>
+      </c>
+      <c r="J23" s="19" t="n">
+        <v>-66.5945609096971</v>
+      </c>
+      <c r="K23" s="20" t="n">
+        <v>-0.00183751611847641</v>
+      </c>
+      <c r="L23" s="19" t="n">
+        <v>-66.5945609096971</v>
+      </c>
+      <c r="M23" s="20" t="n">
+        <v>-0.00183751611847641</v>
+      </c>
+      <c r="N23" s="19" t="n">
+        <v>-118.191797536987</v>
+      </c>
+      <c r="O23" s="20" t="n">
+        <v>-0.00168035422302161</v>
+      </c>
+      <c r="P23" s="19" t="n">
+        <v>-118.191797536987</v>
+      </c>
+      <c r="Q23" s="20" t="n">
+        <v>-0.00168035422302161</v>
+      </c>
+      <c r="R23" s="19" t="n">
+        <v>-75.9014713695411</v>
+      </c>
+      <c r="S23" s="20" t="n">
+        <v>-0.00173633143315576</v>
+      </c>
+      <c r="T23" s="19" t="n">
+        <v>-75.9014713695411</v>
+      </c>
+      <c r="U23" s="20" t="n">
+        <v>-0.00173633143315576</v>
+      </c>
+      <c r="V23" s="19" t="n">
+        <v>-57.5186567808136</v>
+      </c>
+      <c r="W23" s="20" t="n">
+        <v>-0.00184125043994216</v>
+      </c>
+      <c r="X23" s="19" t="n">
+        <v>-57.5186567808136</v>
+      </c>
+      <c r="Y23" s="20" t="n">
+        <v>-0.00184125043994216</v>
+      </c>
+      <c r="Z23" s="19" t="n">
+        <v>-62.1607006556745</v>
+      </c>
+      <c r="AA23" s="41" t="n">
+        <v>-0.00194393854070136</v>
+      </c>
+      <c r="AB23" s="19" t="n">
+        <v>-62.1607006556745</v>
+      </c>
+      <c r="AC23" s="20" t="n">
+        <v>-0.00194393854070136</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="O12" s="28"/>
-      <c r="P12" s="28"/>
-      <c r="Q12" s="28"/>
-      <c r="R12" s="28" t="s">
-        <v>16</v>
-      </c>
-      <c r="S12" s="28"/>
-      <c r="T12" s="28"/>
-      <c r="U12" s="28"/>
-      <c r="V12" s="27" t="s">
-        <v>17</v>
-      </c>
-      <c r="W12" s="27"/>
-      <c r="X12" s="27"/>
-      <c r="Y12" s="27"/>
-      <c r="Z12" s="27" t="s">
-        <v>18</v>
-      </c>
-      <c r="AA12" s="27"/>
-      <c r="AB12" s="27"/>
-      <c r="AC12" s="27"/>
-    </row>
-    <row r="13" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="B13" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="C13" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="D13" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="E13" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="F13" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="G13" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="H13" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="I13" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="J13" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="K13" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="L13" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="M13" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="N13" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="O13" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="P13" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q13" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="R13" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="S13" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="T13" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="U13" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="V13" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="W13" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="X13" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y13" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z13" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA13" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="AB13" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC13" s="9" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="10"/>
-      <c r="B14" s="29"/>
-      <c r="C14" s="30"/>
-      <c r="D14" s="29"/>
-      <c r="E14" s="30"/>
-      <c r="F14" s="29"/>
-      <c r="G14" s="30"/>
-      <c r="H14" s="29"/>
-      <c r="I14" s="30"/>
-      <c r="J14" s="29"/>
-      <c r="K14" s="30"/>
-      <c r="L14" s="29"/>
-      <c r="M14" s="30"/>
-      <c r="N14" s="29"/>
-      <c r="O14" s="30"/>
-      <c r="P14" s="29"/>
-      <c r="Q14" s="30"/>
-      <c r="R14" s="29"/>
-      <c r="S14" s="30"/>
-      <c r="T14" s="29"/>
-      <c r="U14" s="30"/>
-      <c r="V14" s="29"/>
-      <c r="W14" s="30"/>
-      <c r="X14" s="29"/>
-      <c r="Y14" s="30"/>
-      <c r="Z14" s="29"/>
-      <c r="AA14" s="30"/>
-      <c r="AB14" s="29"/>
-      <c r="AC14" s="30"/>
-    </row>
-    <row r="15" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="11"/>
-      <c r="B15" s="11"/>
-      <c r="C15" s="31"/>
-      <c r="D15" s="11"/>
-      <c r="E15" s="31"/>
-      <c r="F15" s="11"/>
-      <c r="G15" s="32"/>
-      <c r="H15" s="32"/>
-      <c r="I15" s="32"/>
-      <c r="J15" s="11"/>
-      <c r="K15" s="32"/>
-      <c r="L15" s="32"/>
-      <c r="M15" s="32"/>
-      <c r="N15" s="11"/>
-      <c r="O15" s="32"/>
-      <c r="P15" s="32"/>
-      <c r="Q15" s="32"/>
-      <c r="R15" s="11"/>
-      <c r="S15" s="32"/>
-      <c r="T15" s="32"/>
-      <c r="U15" s="32"/>
-      <c r="V15" s="11"/>
-      <c r="W15" s="32"/>
-      <c r="X15" s="32"/>
-      <c r="Y15" s="32"/>
-      <c r="Z15" s="11"/>
-      <c r="AA15" s="32"/>
-      <c r="AB15" s="32"/>
-      <c r="AC15" s="32"/>
-    </row>
-    <row r="16" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="B16" s="11"/>
-      <c r="C16" s="31"/>
-      <c r="D16" s="11"/>
-      <c r="E16" s="31"/>
-      <c r="F16" s="11"/>
-      <c r="G16" s="32"/>
-      <c r="H16" s="32"/>
-      <c r="I16" s="32"/>
-      <c r="J16" s="11"/>
-      <c r="K16" s="32"/>
-      <c r="L16" s="32"/>
-      <c r="M16" s="32"/>
-      <c r="N16" s="11"/>
-      <c r="O16" s="32"/>
-      <c r="P16" s="32"/>
-      <c r="Q16" s="32"/>
-      <c r="R16" s="11"/>
-      <c r="S16" s="32"/>
-      <c r="T16" s="32"/>
-      <c r="U16" s="32"/>
-      <c r="V16" s="11"/>
-      <c r="W16" s="32"/>
-      <c r="X16" s="32"/>
-      <c r="Y16" s="32"/>
-      <c r="Z16" s="11"/>
-      <c r="AA16" s="32"/>
-      <c r="AB16" s="32"/>
-      <c r="AC16" s="32"/>
-    </row>
-    <row r="17" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="13"/>
-      <c r="B17" s="13"/>
-      <c r="C17" s="33"/>
-      <c r="D17" s="13"/>
-      <c r="E17" s="33"/>
-      <c r="F17" s="13"/>
-      <c r="G17" s="34"/>
-      <c r="H17" s="34"/>
-      <c r="I17" s="34"/>
-      <c r="J17" s="13"/>
-      <c r="K17" s="34"/>
-      <c r="L17" s="34"/>
-      <c r="M17" s="34"/>
-      <c r="N17" s="13"/>
-      <c r="O17" s="34"/>
-      <c r="P17" s="34"/>
-      <c r="Q17" s="34"/>
-      <c r="R17" s="13"/>
-      <c r="S17" s="34"/>
-      <c r="T17" s="34"/>
-      <c r="U17" s="34"/>
-      <c r="V17" s="13"/>
-      <c r="W17" s="34"/>
-      <c r="X17" s="34"/>
-      <c r="Y17" s="34"/>
-      <c r="Z17" s="13"/>
-      <c r="AA17" s="34"/>
-      <c r="AB17" s="34"/>
-      <c r="AC17" s="34"/>
-    </row>
-    <row r="18" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="14" t="s">
-        <v>7</v>
-      </c>
-      <c r="B18" s="35" t="n">
-        <v>1890146.68</v>
-      </c>
-      <c r="C18" s="36" t="n">
-        <v>1</v>
-      </c>
-      <c r="D18" s="35" t="n">
-        <v>1890146.68</v>
-      </c>
-      <c r="E18" s="36" t="n">
-        <v>1</v>
-      </c>
-      <c r="F18" s="37" t="n">
-        <v>56113.91</v>
-      </c>
-      <c r="G18" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="H18" s="35" t="n">
-        <v>56113.91</v>
-      </c>
-      <c r="I18" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="J18" s="37" t="n">
-        <v>36241.62</v>
-      </c>
-      <c r="K18" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="L18" s="35" t="n">
-        <v>36241.62</v>
-      </c>
-      <c r="M18" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="N18" s="37" t="n">
-        <v>70337.43</v>
-      </c>
-      <c r="O18" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="P18" s="35" t="n">
-        <v>70337.43</v>
-      </c>
-      <c r="Q18" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="R18" s="37" t="n">
-        <v>43713.7</v>
-      </c>
-      <c r="S18" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="T18" s="35" t="n">
-        <v>43713.7</v>
-      </c>
-      <c r="U18" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="V18" s="35" t="n">
-        <v>31238.91</v>
-      </c>
-      <c r="W18" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="X18" s="35" t="n">
-        <v>31238.91</v>
-      </c>
-      <c r="Y18" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z18" s="35" t="n">
-        <v>31976.68</v>
-      </c>
-      <c r="AA18" s="39" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB18" s="35" t="n">
-        <v>31976.68</v>
-      </c>
-      <c r="AC18" s="38" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="10"/>
-      <c r="B19" s="40"/>
-      <c r="C19" s="41"/>
-      <c r="D19" s="40"/>
-      <c r="E19" s="41"/>
-      <c r="F19" s="35"/>
-      <c r="G19" s="42"/>
-      <c r="H19" s="40"/>
-      <c r="I19" s="42"/>
-      <c r="J19" s="35"/>
-      <c r="K19" s="42"/>
-      <c r="L19" s="40"/>
-      <c r="M19" s="42"/>
-      <c r="N19" s="35"/>
-      <c r="O19" s="42"/>
-      <c r="P19" s="40"/>
-      <c r="Q19" s="42"/>
-      <c r="R19" s="35"/>
-      <c r="S19" s="42"/>
-      <c r="T19" s="40"/>
-      <c r="U19" s="42"/>
-      <c r="V19" s="40"/>
-      <c r="W19" s="42"/>
-      <c r="X19" s="40"/>
-      <c r="Y19" s="42"/>
-      <c r="Z19" s="40"/>
-      <c r="AA19" s="43"/>
-      <c r="AB19" s="40"/>
-      <c r="AC19" s="42"/>
-    </row>
-    <row r="20" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="B20" s="44"/>
-      <c r="C20" s="24"/>
-      <c r="D20" s="3"/>
-      <c r="E20" s="24"/>
-      <c r="F20" s="3"/>
-      <c r="G20" s="25"/>
-      <c r="H20" s="3"/>
-      <c r="I20" s="25"/>
-      <c r="J20" s="3"/>
-      <c r="K20" s="25"/>
-      <c r="L20" s="3"/>
-      <c r="M20" s="25"/>
-      <c r="N20" s="3"/>
-      <c r="O20" s="25"/>
-      <c r="P20" s="3"/>
-      <c r="Q20" s="25"/>
-      <c r="R20" s="3"/>
-      <c r="S20" s="25"/>
-      <c r="T20" s="3"/>
-      <c r="U20" s="25"/>
-      <c r="V20" s="3"/>
-      <c r="W20" s="25"/>
-      <c r="X20" s="3"/>
-      <c r="Y20" s="25"/>
-      <c r="Z20" s="3"/>
-      <c r="AA20" s="45"/>
-      <c r="AB20" s="3"/>
-      <c r="AC20" s="25"/>
-    </row>
-    <row r="21" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="B21" s="3"/>
-      <c r="C21" s="24"/>
-      <c r="D21" s="3"/>
-      <c r="E21" s="24"/>
-      <c r="F21" s="3"/>
-      <c r="G21" s="25"/>
-      <c r="H21" s="3"/>
-      <c r="I21" s="25"/>
-      <c r="J21" s="3"/>
-      <c r="K21" s="25"/>
-      <c r="L21" s="3"/>
-      <c r="M21" s="25"/>
-      <c r="N21" s="3"/>
-      <c r="O21" s="25"/>
-      <c r="P21" s="3"/>
-      <c r="Q21" s="25"/>
-      <c r="R21" s="3"/>
-      <c r="S21" s="25"/>
-      <c r="T21" s="3"/>
-      <c r="U21" s="25"/>
-      <c r="V21" s="3"/>
-      <c r="W21" s="25"/>
-      <c r="X21" s="3"/>
-      <c r="Y21" s="25"/>
-      <c r="Z21" s="3"/>
-      <c r="AA21" s="45"/>
-      <c r="AB21" s="3"/>
-      <c r="AC21" s="25"/>
-    </row>
-    <row r="22" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="B22" s="35" t="n">
-        <v>49887.7048682951</v>
-      </c>
-      <c r="C22" s="36" t="n">
-        <v>0.0263935626775246</v>
-      </c>
-      <c r="D22" s="35" t="n">
-        <v>49887.7048682951</v>
-      </c>
-      <c r="E22" s="36" t="n">
-        <v>0.0263935626775246</v>
-      </c>
-      <c r="F22" s="35" t="n">
-        <v>1705.6561549394</v>
-      </c>
-      <c r="G22" s="36" t="n">
-        <v>0.0303963162598971</v>
-      </c>
-      <c r="H22" s="35" t="n">
-        <v>1705.6561549394</v>
-      </c>
-      <c r="I22" s="36" t="n">
-        <v>0.0303963162598971</v>
-      </c>
-      <c r="J22" s="35" t="n">
-        <v>1227.87225264468</v>
-      </c>
-      <c r="K22" s="36" t="n">
-        <v>0.0338801701647079</v>
-      </c>
-      <c r="L22" s="35" t="n">
-        <v>1227.87225264468</v>
-      </c>
-      <c r="M22" s="36" t="n">
-        <v>0.0338801701647079</v>
-      </c>
-      <c r="N22" s="35" t="n">
-        <v>2199.83862997688</v>
-      </c>
-      <c r="O22" s="36" t="n">
-        <v>0.0312755048055763</v>
-      </c>
-      <c r="P22" s="35" t="n">
-        <v>2199.83862997688</v>
-      </c>
-      <c r="Q22" s="36" t="n">
-        <v>0.0312755048055763</v>
-      </c>
-      <c r="R22" s="35" t="n">
-        <v>1232.71175827654</v>
-      </c>
-      <c r="S22" s="36" t="n">
-        <v>0.0281996664266932</v>
-      </c>
-      <c r="T22" s="35" t="n">
-        <v>1232.71175827654</v>
-      </c>
-      <c r="U22" s="36" t="n">
-        <v>0.0281996664266932</v>
-      </c>
-      <c r="V22" s="35" t="n">
-        <v>872.765729625539</v>
-      </c>
-      <c r="W22" s="36" t="n">
-        <v>0.0279384181338446</v>
-      </c>
-      <c r="X22" s="35" t="n">
-        <v>872.765729625539</v>
-      </c>
-      <c r="Y22" s="36" t="n">
-        <v>0.0279384181338446</v>
-      </c>
-      <c r="Z22" s="35" t="n">
-        <v>1231.87636658085</v>
-      </c>
-      <c r="AA22" s="46" t="n">
-        <v>0.0385242109743992</v>
-      </c>
-      <c r="AB22" s="35" t="n">
-        <v>1231.87636658085</v>
-      </c>
-      <c r="AC22" s="36" t="n">
-        <v>0.0385242109743992</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="B23" s="35" t="n">
-        <v>-3390.80544821547</v>
-      </c>
-      <c r="C23" s="36" t="n">
-        <v>-0.00179393773197299</v>
-      </c>
-      <c r="D23" s="35" t="n">
-        <v>-3390.80544821547</v>
-      </c>
-      <c r="E23" s="36" t="n">
-        <v>-0.00179393773197299</v>
-      </c>
-      <c r="F23" s="35" t="n">
-        <v>-95.6776850726545</v>
-      </c>
-      <c r="G23" s="36" t="n">
-        <v>-0.00170506181217196</v>
-      </c>
-      <c r="H23" s="35" t="n">
-        <v>-95.6776850726545</v>
-      </c>
-      <c r="I23" s="36" t="n">
-        <v>-0.00170506181217196</v>
-      </c>
-      <c r="J23" s="35" t="n">
-        <v>-66.5945609096971</v>
-      </c>
-      <c r="K23" s="36" t="n">
-        <v>-0.00183751611847641</v>
-      </c>
-      <c r="L23" s="35" t="n">
-        <v>-66.5945609096971</v>
-      </c>
-      <c r="M23" s="36" t="n">
-        <v>-0.00183751611847641</v>
-      </c>
-      <c r="N23" s="35" t="n">
-        <v>-118.191797536987</v>
-      </c>
-      <c r="O23" s="36" t="n">
-        <v>-0.00168035422302161</v>
-      </c>
-      <c r="P23" s="35" t="n">
-        <v>-118.191797536987</v>
-      </c>
-      <c r="Q23" s="36" t="n">
-        <v>-0.00168035422302161</v>
-      </c>
-      <c r="R23" s="35" t="n">
-        <v>-75.9014713695411</v>
-      </c>
-      <c r="S23" s="36" t="n">
-        <v>-0.00173633143315576</v>
-      </c>
-      <c r="T23" s="35" t="n">
-        <v>-75.9014713695411</v>
-      </c>
-      <c r="U23" s="36" t="n">
-        <v>-0.00173633143315576</v>
-      </c>
-      <c r="V23" s="35" t="n">
-        <v>-57.5186567808136</v>
-      </c>
-      <c r="W23" s="36" t="n">
-        <v>-0.00184125043994216</v>
-      </c>
-      <c r="X23" s="35" t="n">
-        <v>-57.5186567808136</v>
-      </c>
-      <c r="Y23" s="36" t="n">
-        <v>-0.00184125043994216</v>
-      </c>
-      <c r="Z23" s="35" t="n">
-        <v>-62.1607006556745</v>
-      </c>
-      <c r="AA23" s="46" t="n">
-        <v>-0.00194393854070136</v>
-      </c>
-      <c r="AB23" s="35" t="n">
-        <v>-62.1607006556745</v>
-      </c>
-      <c r="AC23" s="36" t="n">
-        <v>-0.00194393854070136</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="B24" s="35" t="n">
+      <c r="B24" s="19" t="n">
         <v>128564.289829883</v>
       </c>
-      <c r="C24" s="36" t="n">
+      <c r="C24" s="20" t="n">
         <v>0.0680181549877828</v>
       </c>
-      <c r="D24" s="35" t="n">
+      <c r="D24" s="19" t="n">
         <v>128564.289829883</v>
       </c>
-      <c r="E24" s="36" t="n">
+      <c r="E24" s="20" t="n">
         <v>0.0680181549877828</v>
       </c>
-      <c r="F24" s="35" t="n">
+      <c r="F24" s="19" t="n">
         <v>3658.20212926082</v>
       </c>
-      <c r="G24" s="36" t="n">
+      <c r="G24" s="20" t="n">
         <v>0.0651924296357323</v>
       </c>
-      <c r="H24" s="35" t="n">
+      <c r="H24" s="19" t="n">
         <v>3658.20212926082</v>
       </c>
-      <c r="I24" s="36" t="n">
+      <c r="I24" s="20" t="n">
         <v>0.0651924296357323</v>
       </c>
-      <c r="J24" s="35" t="n">
+      <c r="J24" s="19" t="n">
         <v>2482.02750258874</v>
       </c>
-      <c r="K24" s="36" t="n">
+      <c r="K24" s="20" t="n">
         <v>0.0684855561806767</v>
       </c>
-      <c r="L24" s="35" t="n">
+      <c r="L24" s="19" t="n">
         <v>2482.02750258874</v>
       </c>
-      <c r="M24" s="36" t="n">
+      <c r="M24" s="20" t="n">
         <v>0.0684855561806767</v>
       </c>
-      <c r="N24" s="35" t="n">
+      <c r="N24" s="19" t="n">
         <v>4671.56634812652</v>
       </c>
-      <c r="O24" s="36" t="n">
+      <c r="O24" s="20" t="n">
         <v>0.0664165060925104</v>
       </c>
-      <c r="P24" s="35" t="n">
+      <c r="P24" s="19" t="n">
         <v>4671.56634812652</v>
       </c>
-      <c r="Q24" s="36" t="n">
+      <c r="Q24" s="20" t="n">
         <v>0.0664165060925104</v>
       </c>
-      <c r="R24" s="35" t="n">
+      <c r="R24" s="19" t="n">
         <v>2900.10056130042</v>
       </c>
-      <c r="S24" s="36" t="n">
+      <c r="S24" s="20" t="n">
         <v>0.0663430586132134</v>
       </c>
-      <c r="T24" s="35" t="n">
+      <c r="T24" s="19" t="n">
         <v>2900.10056130042</v>
       </c>
-      <c r="U24" s="36" t="n">
+      <c r="U24" s="20" t="n">
         <v>0.0663430586132134</v>
       </c>
-      <c r="V24" s="35" t="n">
+      <c r="V24" s="19" t="n">
         <v>1929.17640382092</v>
       </c>
-      <c r="W24" s="36" t="n">
+      <c r="W24" s="20" t="n">
         <v>0.0617555607356632</v>
       </c>
-      <c r="X24" s="35" t="n">
+      <c r="X24" s="19" t="n">
         <v>1929.17640382092</v>
       </c>
-      <c r="Y24" s="36" t="n">
+      <c r="Y24" s="20" t="n">
         <v>0.0617555607356632</v>
       </c>
-      <c r="Z24" s="35" t="n">
+      <c r="Z24" s="19" t="n">
         <v>2236.15816435266</v>
       </c>
-      <c r="AA24" s="46" t="n">
+      <c r="AA24" s="41" t="n">
         <v>0.0699309047828811</v>
       </c>
-      <c r="AB24" s="35" t="n">
+      <c r="AB24" s="19" t="n">
         <v>2236.15816435266</v>
       </c>
-      <c r="AC24" s="36" t="n">
+      <c r="AC24" s="20" t="n">
         <v>0.0699309047828811</v>
       </c>
     </row>
@@ -2050,33 +1997,33 @@
   <dimension ref="A1:A6"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
-    <row r="1" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+    <row r="1" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="1" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
+    <row r="3" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="1" t="s">
         <v>2</v>
       </c>
     </row>
